--- a/backend/data/financials_by_company/1326.HK.xlsx
+++ b/backend/data/financials_by_company/1326.HK.xlsx
@@ -667,55 +667,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-7987778.157299</v>
+        <v>56124116.743472</v>
       </c>
       <c r="C2" t="n">
-        <v>0.029803</v>
+        <v>0.398654</v>
       </c>
       <c r="D2" t="n">
-        <v>-244137000</v>
+        <v>73100000</v>
       </c>
       <c r="E2" t="n">
-        <v>-44229000</v>
+        <v>140784000</v>
       </c>
       <c r="F2" t="n">
-        <v>-268021000</v>
+        <v>140784000</v>
       </c>
       <c r="G2" t="n">
-        <v>-350510000</v>
+        <v>-7633000</v>
       </c>
       <c r="H2" t="n">
-        <v>70530000</v>
+        <v>132831000</v>
       </c>
       <c r="I2" t="n">
-        <v>364020000</v>
+        <v>325857000</v>
       </c>
       <c r="J2" t="n">
-        <v>-288366000</v>
+        <v>213884000</v>
       </c>
       <c r="K2" t="n">
-        <v>-358896000</v>
+        <v>81053000</v>
       </c>
       <c r="L2" t="n">
-        <v>-12272000</v>
+        <v>-66344000</v>
       </c>
       <c r="M2" t="n">
-        <v>14089000</v>
+        <v>67382000</v>
       </c>
       <c r="N2" t="n">
-        <v>1817000</v>
+        <v>1038000</v>
       </c>
       <c r="O2" t="n">
-        <v>133315221.842701</v>
+        <v>-92292883.25652801</v>
       </c>
       <c r="P2" t="n">
-        <v>-350510000</v>
+        <v>-7633000</v>
       </c>
       <c r="Q2" t="n">
-        <v>385186000</v>
+        <v>518470000</v>
       </c>
       <c r="R2" t="n">
         <v>2595613733</v>
@@ -724,145 +724,147 @@
         <v>2595613733</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.135</v>
+        <v>-0.0029</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.135</v>
+        <v>-0.0029</v>
       </c>
       <c r="V2" t="n">
-        <v>-350510000</v>
+        <v>-7633000</v>
       </c>
       <c r="W2" t="n">
-        <v>-350510000</v>
+        <v>-7633000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-350510000</v>
+        <v>-7633000</v>
       </c>
       <c r="Z2" t="n">
-        <v>11359000</v>
+        <v>-15854000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-361869000</v>
+        <v>8221000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-361869000</v>
+        <v>8221000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-11116000</v>
+        <v>5450000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-372985000</v>
+        <v>13671000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-109000</v>
+        <v>1268000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-268021000</v>
+        <v>136003000</v>
       </c>
       <c r="AG2" t="n">
-        <v>5565000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-134735000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-44000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>32841000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5823000</v>
+        <v>-1268000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-12272000</v>
+        <v>-66344000</v>
       </c>
       <c r="AL2" t="n">
-        <v>14089000</v>
+        <v>67382000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1817000</v>
+        <v>1038000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-92583000</v>
+        <v>-61482000</v>
       </c>
       <c r="AO2" t="n">
-        <v>21166000</v>
+        <v>192613000</v>
       </c>
       <c r="AP2" t="n">
-        <v>647000</v>
+        <v>-44000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>119212000</v>
+        <v>241866000</v>
       </c>
       <c r="AR2" t="n">
-        <v>65283000</v>
+        <v>159453000</v>
       </c>
       <c r="AS2" t="n">
-        <v>53929000</v>
+        <v>82413000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-71417000</v>
+        <v>131131000</v>
       </c>
       <c r="AU2" t="n">
-        <v>364020000</v>
+        <v>325857000</v>
       </c>
       <c r="AV2" t="n">
-        <v>292603000</v>
+        <v>456988000</v>
       </c>
       <c r="AW2" t="n">
-        <v>292603000</v>
+        <v>456988000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-1512210.373842</v>
+        <v>-20711750</v>
       </c>
       <c r="C3" t="n">
-        <v>0.012121</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-88314000</v>
+        <v>32952000</v>
       </c>
       <c r="E3" t="n">
-        <v>-6962000</v>
+        <v>-15195000</v>
       </c>
       <c r="F3" t="n">
-        <v>-124764000</v>
+        <v>-82847000</v>
       </c>
       <c r="G3" t="n">
-        <v>-186920000</v>
+        <v>-92166000</v>
       </c>
       <c r="H3" t="n">
-        <v>73914000</v>
+        <v>76558000</v>
       </c>
       <c r="I3" t="n">
-        <v>120238000</v>
+        <v>577836000</v>
       </c>
       <c r="J3" t="n">
-        <v>-95276000</v>
+        <v>17757000</v>
       </c>
       <c r="K3" t="n">
-        <v>-169190000</v>
+        <v>-58801000</v>
       </c>
       <c r="L3" t="n">
-        <v>-16552000</v>
+        <v>-22655000</v>
       </c>
       <c r="M3" t="n">
-        <v>18590000</v>
+        <v>23365000</v>
       </c>
       <c r="N3" t="n">
-        <v>2038000</v>
+        <v>710000</v>
       </c>
       <c r="O3" t="n">
-        <v>54133789.626158</v>
+        <v>37621250</v>
       </c>
       <c r="P3" t="n">
-        <v>-186920000</v>
+        <v>-92166000</v>
       </c>
       <c r="Q3" t="n">
-        <v>211633000</v>
+        <v>679458000</v>
       </c>
       <c r="R3" t="n">
         <v>2595613733</v>
@@ -871,147 +873,145 @@
         <v>2595613733</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0355</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0355</v>
       </c>
       <c r="V3" t="n">
-        <v>-186920000</v>
+        <v>-92166000</v>
       </c>
       <c r="W3" t="n">
-        <v>-186920000</v>
+        <v>-92166000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-186920000</v>
+        <v>-92166000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1416000</v>
+        <v>-3026000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-185504000</v>
+        <v>-89140000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-185504000</v>
+        <v>-89140000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2276000</v>
+        <v>6974000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-187780000</v>
+        <v>-82166000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-8538000</v>
+        <v>-242000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-121341000</v>
+        <v>-66044000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4999000</v>
+        <v>-79000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2361000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
+        <v>998000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>8538000</v>
+        <v>-1529000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-16552000</v>
+        <v>-22655000</v>
       </c>
       <c r="AL3" t="n">
-        <v>18590000</v>
+        <v>23365000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2038000</v>
+        <v>710000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-45204000</v>
+        <v>24523000</v>
       </c>
       <c r="AO3" t="n">
-        <v>91395000</v>
+        <v>101622000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2361000</v>
+        <v>998000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>140427000</v>
+        <v>166859000</v>
       </c>
       <c r="AR3" t="n">
-        <v>74928000</v>
+        <v>84225000</v>
       </c>
       <c r="AS3" t="n">
-        <v>65499000</v>
+        <v>82634000</v>
       </c>
       <c r="AT3" t="n">
-        <v>46191000</v>
+        <v>126145000</v>
       </c>
       <c r="AU3" t="n">
-        <v>120238000</v>
+        <v>577836000</v>
       </c>
       <c r="AV3" t="n">
-        <v>166429000</v>
+        <v>703981000</v>
       </c>
       <c r="AW3" t="n">
-        <v>166429000</v>
+        <v>703981000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-20711750</v>
+        <v>-1512210.373842</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.012121</v>
       </c>
       <c r="D4" t="n">
-        <v>32952000</v>
+        <v>-88314000</v>
       </c>
       <c r="E4" t="n">
-        <v>-15195000</v>
+        <v>-6962000</v>
       </c>
       <c r="F4" t="n">
-        <v>-82847000</v>
+        <v>-124764000</v>
       </c>
       <c r="G4" t="n">
-        <v>-92166000</v>
+        <v>-186920000</v>
       </c>
       <c r="H4" t="n">
-        <v>76558000</v>
+        <v>73914000</v>
       </c>
       <c r="I4" t="n">
-        <v>577836000</v>
+        <v>120238000</v>
       </c>
       <c r="J4" t="n">
-        <v>17757000</v>
+        <v>-95276000</v>
       </c>
       <c r="K4" t="n">
-        <v>-58801000</v>
+        <v>-169190000</v>
       </c>
       <c r="L4" t="n">
-        <v>-22655000</v>
+        <v>-16552000</v>
       </c>
       <c r="M4" t="n">
-        <v>23365000</v>
+        <v>18590000</v>
       </c>
       <c r="N4" t="n">
-        <v>710000</v>
+        <v>2038000</v>
       </c>
       <c r="O4" t="n">
-        <v>37621250</v>
+        <v>54133789.626158</v>
       </c>
       <c r="P4" t="n">
-        <v>-92166000</v>
+        <v>-186920000</v>
       </c>
       <c r="Q4" t="n">
-        <v>679458000</v>
+        <v>211633000</v>
       </c>
       <c r="R4" t="n">
         <v>2595613733</v>
@@ -1020,145 +1020,147 @@
         <v>2595613733</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0355</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0355</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-92166000</v>
+        <v>-186920000</v>
       </c>
       <c r="W4" t="n">
-        <v>-92166000</v>
+        <v>-186920000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-92166000</v>
+        <v>-186920000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3026000</v>
+        <v>-1416000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-89140000</v>
+        <v>-185504000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-89140000</v>
+        <v>-185504000</v>
       </c>
       <c r="AC4" t="n">
-        <v>6974000</v>
+        <v>-2276000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-82166000</v>
+        <v>-187780000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-242000</v>
+        <v>-8538000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-66044000</v>
+        <v>-121341000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-79000</v>
+        <v>-4999000</v>
       </c>
       <c r="AH4" t="n">
-        <v>998000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>-2361000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-1529000</v>
+        <v>8538000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-22655000</v>
+        <v>-16552000</v>
       </c>
       <c r="AL4" t="n">
-        <v>23365000</v>
+        <v>18590000</v>
       </c>
       <c r="AM4" t="n">
-        <v>710000</v>
+        <v>2038000</v>
       </c>
       <c r="AN4" t="n">
-        <v>24523000</v>
+        <v>-45204000</v>
       </c>
       <c r="AO4" t="n">
-        <v>101622000</v>
+        <v>91395000</v>
       </c>
       <c r="AP4" t="n">
-        <v>998000</v>
+        <v>-2361000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>166859000</v>
+        <v>140427000</v>
       </c>
       <c r="AR4" t="n">
-        <v>84225000</v>
+        <v>74928000</v>
       </c>
       <c r="AS4" t="n">
-        <v>82634000</v>
+        <v>65499000</v>
       </c>
       <c r="AT4" t="n">
-        <v>126145000</v>
+        <v>46191000</v>
       </c>
       <c r="AU4" t="n">
-        <v>577836000</v>
+        <v>120238000</v>
       </c>
       <c r="AV4" t="n">
-        <v>703981000</v>
+        <v>166429000</v>
       </c>
       <c r="AW4" t="n">
-        <v>703981000</v>
+        <v>166429000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>56124116.743472</v>
+        <v>-7987778.157299</v>
       </c>
       <c r="C5" t="n">
-        <v>0.398654</v>
+        <v>0.029803</v>
       </c>
       <c r="D5" t="n">
-        <v>73100000</v>
+        <v>-244137000</v>
       </c>
       <c r="E5" t="n">
-        <v>140784000</v>
+        <v>-44229000</v>
       </c>
       <c r="F5" t="n">
-        <v>140784000</v>
+        <v>-268021000</v>
       </c>
       <c r="G5" t="n">
-        <v>-7633000</v>
+        <v>-350510000</v>
       </c>
       <c r="H5" t="n">
-        <v>132831000</v>
+        <v>70530000</v>
       </c>
       <c r="I5" t="n">
-        <v>325857000</v>
+        <v>364020000</v>
       </c>
       <c r="J5" t="n">
-        <v>213884000</v>
+        <v>-288366000</v>
       </c>
       <c r="K5" t="n">
-        <v>81053000</v>
+        <v>-358896000</v>
       </c>
       <c r="L5" t="n">
-        <v>-66344000</v>
+        <v>-12272000</v>
       </c>
       <c r="M5" t="n">
-        <v>67382000</v>
+        <v>14089000</v>
       </c>
       <c r="N5" t="n">
-        <v>1038000</v>
+        <v>1817000</v>
       </c>
       <c r="O5" t="n">
-        <v>-92292883.25652801</v>
+        <v>133315221.842701</v>
       </c>
       <c r="P5" t="n">
-        <v>-7633000</v>
+        <v>-350510000</v>
       </c>
       <c r="Q5" t="n">
-        <v>518470000</v>
+        <v>385186000</v>
       </c>
       <c r="R5" t="n">
         <v>2595613733</v>
@@ -1167,94 +1169,92 @@
         <v>2595613733</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0029</v>
+        <v>-0.135</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0029</v>
+        <v>-0.135</v>
       </c>
       <c r="V5" t="n">
-        <v>-7633000</v>
+        <v>-350510000</v>
       </c>
       <c r="W5" t="n">
-        <v>-7633000</v>
+        <v>-350510000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-7633000</v>
+        <v>-350510000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-15854000</v>
+        <v>11359000</v>
       </c>
       <c r="AA5" t="n">
-        <v>8221000</v>
+        <v>-361869000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8221000</v>
+        <v>-361869000</v>
       </c>
       <c r="AC5" t="n">
-        <v>5450000</v>
+        <v>-11116000</v>
       </c>
       <c r="AD5" t="n">
-        <v>13671000</v>
+        <v>-372985000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1268000</v>
+        <v>-109000</v>
       </c>
       <c r="AF5" t="n">
-        <v>136003000</v>
+        <v>-268021000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-134735000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-44000</v>
-      </c>
+        <v>5565000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>32841000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1268000</v>
+        <v>5823000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-66344000</v>
+        <v>-12272000</v>
       </c>
       <c r="AL5" t="n">
-        <v>67382000</v>
+        <v>14089000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1038000</v>
+        <v>1817000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-61482000</v>
+        <v>-92583000</v>
       </c>
       <c r="AO5" t="n">
-        <v>192613000</v>
+        <v>21166000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-44000</v>
+        <v>647000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>241866000</v>
+        <v>119212000</v>
       </c>
       <c r="AR5" t="n">
-        <v>159453000</v>
+        <v>65283000</v>
       </c>
       <c r="AS5" t="n">
-        <v>82413000</v>
+        <v>53929000</v>
       </c>
       <c r="AT5" t="n">
-        <v>131131000</v>
+        <v>-71417000</v>
       </c>
       <c r="AU5" t="n">
-        <v>325857000</v>
+        <v>364020000</v>
       </c>
       <c r="AV5" t="n">
-        <v>456988000</v>
+        <v>292603000</v>
       </c>
       <c r="AW5" t="n">
-        <v>456988000</v>
+        <v>292603000</v>
       </c>
     </row>
   </sheetData>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>2595613733</v>
@@ -1644,50 +1644,46 @@
         <v>2595613733</v>
       </c>
       <c r="D2" t="n">
-        <v>106823000</v>
+        <v>247874000</v>
       </c>
       <c r="E2" t="n">
-        <v>175102000</v>
+        <v>576365000</v>
       </c>
       <c r="F2" t="n">
-        <v>-247735000</v>
+        <v>-369623000</v>
       </c>
       <c r="G2" t="n">
-        <v>-60973000</v>
+        <v>546762000</v>
       </c>
       <c r="H2" t="n">
-        <v>-140876000</v>
+        <v>-31314000</v>
       </c>
       <c r="I2" t="n">
-        <v>-247735000</v>
+        <v>-369623000</v>
       </c>
       <c r="J2" t="n">
-        <v>9291000</v>
+        <v>224668000</v>
       </c>
       <c r="K2" t="n">
-        <v>-226784000</v>
+        <v>195065000</v>
       </c>
       <c r="L2" t="n">
-        <v>-154914000</v>
+        <v>453898000</v>
       </c>
       <c r="M2" t="n">
-        <v>-185098000</v>
+        <v>249808000</v>
       </c>
       <c r="N2" t="n">
-        <v>41686000</v>
+        <v>54743000</v>
       </c>
       <c r="O2" t="n">
-        <v>-226784000</v>
+        <v>195065000</v>
       </c>
       <c r="P2" t="n">
-        <v>457862000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1203189000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>521046000</v>
-      </c>
+        <v>204600000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>6489000</v>
       </c>
@@ -1695,146 +1691,166 @@
         <v>6489000</v>
       </c>
       <c r="U2" t="n">
-        <v>580486000</v>
+        <v>1381072000</v>
       </c>
       <c r="V2" t="n">
-        <v>74778000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>512074000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>71248000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>383000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>323000</v>
+        <v>21215000</v>
       </c>
       <c r="Z2" t="n">
-        <v>74455000</v>
+        <v>419611000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2585000</v>
+        <v>160778000</v>
       </c>
       <c r="AB2" t="n">
-        <v>71870000</v>
+        <v>258833000</v>
       </c>
       <c r="AC2" t="n">
-        <v>505708000</v>
+        <v>868998000</v>
       </c>
       <c r="AD2" t="n">
-        <v>34112000</v>
+        <v>38256000</v>
       </c>
       <c r="AE2" t="n">
-        <v>100647000</v>
+        <v>156754000</v>
       </c>
       <c r="AF2" t="n">
-        <v>6706000</v>
+        <v>63890000</v>
       </c>
       <c r="AG2" t="n">
-        <v>93941000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16791000</v>
-      </c>
+        <v>92864000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>250855000</v>
+        <v>286995000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>186312000</v>
+        <v>188965000</v>
       </c>
       <c r="AK2" t="n">
-        <v>12361000</v>
+        <v>9797000</v>
       </c>
       <c r="AL2" t="n">
-        <v>52182000</v>
+        <v>88233000</v>
       </c>
       <c r="AM2" t="n">
-        <v>395388000</v>
+        <v>1630880000</v>
       </c>
       <c r="AN2" t="n">
-        <v>30556000</v>
+        <v>793196000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+        <v>15089000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>20332000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>155000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>20951000</v>
+        <v>564688000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1293000</v>
+        <v>91325000</v>
       </c>
       <c r="AV2" t="n">
-        <v>19658000</v>
+        <v>473363000</v>
       </c>
       <c r="AW2" t="n">
-        <v>9605000</v>
+        <v>171932000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-280005000</v>
+        <v>-126753000</v>
       </c>
       <c r="AY2" t="n">
-        <v>289610000</v>
+        <v>298685000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>281032000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>281019000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>14120000</v>
+      </c>
       <c r="BB2" t="n">
-        <v>8578000</v>
+        <v>17666000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>364832000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>837684000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
       <c r="BF2" t="n">
-        <v>21212000</v>
+        <v>3566000</v>
       </c>
       <c r="BG2" t="n">
-        <v>11166000</v>
+        <v>21809000</v>
       </c>
       <c r="BH2" t="n">
-        <v>143708000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
+        <v>522643000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3863000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="BK2" t="n">
-        <v>143708000</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
+        <v>518780000</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>3863000</v>
+      </c>
       <c r="BM2" t="n">
-        <v>60773000</v>
+        <v>70897000</v>
       </c>
       <c r="BN2" t="n">
-        <v>5447000</v>
+        <v>26343000</v>
       </c>
       <c r="BO2" t="n">
-        <v>53382000</v>
+        <v>76329000</v>
       </c>
       <c r="BP2" t="n">
-        <v>-1011000</v>
+        <v>-1982000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>54393000</v>
+        <v>78311000</v>
       </c>
       <c r="BR2" t="n">
-        <v>69144000</v>
+        <v>116097000</v>
       </c>
       <c r="BS2" t="n">
-        <v>10156000</v>
+        <v>12274000</v>
       </c>
       <c r="BT2" t="n">
-        <v>58988000</v>
+        <v>103823000</v>
       </c>
       <c r="BU2" t="n">
-        <v>58988000</v>
+        <v>103823000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>2595613733</v>
@@ -1843,50 +1859,46 @@
         <v>2595613733</v>
       </c>
       <c r="D3" t="n">
-        <v>96582000</v>
+        <v>60567000</v>
       </c>
       <c r="E3" t="n">
-        <v>271818000</v>
+        <v>342930000</v>
       </c>
       <c r="F3" t="n">
-        <v>-180790000</v>
+        <v>-122478000</v>
       </c>
       <c r="G3" t="n">
-        <v>295465000</v>
+        <v>506956000</v>
       </c>
       <c r="H3" t="n">
-        <v>-114400000</v>
+        <v>62288000</v>
       </c>
       <c r="I3" t="n">
-        <v>-180790000</v>
+        <v>-122478000</v>
       </c>
       <c r="J3" t="n">
-        <v>90128000</v>
+        <v>178901000</v>
       </c>
       <c r="K3" t="n">
-        <v>113775000</v>
+        <v>342927000</v>
       </c>
       <c r="L3" t="n">
-        <v>187935000</v>
+        <v>373604000</v>
       </c>
       <c r="M3" t="n">
-        <v>167181000</v>
+        <v>399027000</v>
       </c>
       <c r="N3" t="n">
-        <v>53406000</v>
+        <v>56100000</v>
       </c>
       <c r="O3" t="n">
-        <v>113775000</v>
+        <v>342927000</v>
       </c>
       <c r="P3" t="n">
-        <v>448062000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-852679000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>521046000</v>
-      </c>
+        <v>464612000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>6489000</v>
       </c>
@@ -1894,152 +1906,154 @@
         <v>6489000</v>
       </c>
       <c r="U3" t="n">
-        <v>755383000</v>
+        <v>865259000</v>
       </c>
       <c r="V3" t="n">
-        <v>95459000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>264768000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>127509000</v>
+      </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>12210000</v>
+        <v>17896000</v>
       </c>
       <c r="Z3" t="n">
-        <v>83249000</v>
+        <v>119363000</v>
       </c>
       <c r="AA3" t="n">
-        <v>9089000</v>
+        <v>88686000</v>
       </c>
       <c r="AB3" t="n">
-        <v>74160000</v>
+        <v>30677000</v>
       </c>
       <c r="AC3" t="n">
-        <v>659924000</v>
+        <v>600491000</v>
       </c>
       <c r="AD3" t="n">
-        <v>34430000</v>
+        <v>37300000</v>
       </c>
       <c r="AE3" t="n">
-        <v>188569000</v>
+        <v>223567000</v>
       </c>
       <c r="AF3" t="n">
-        <v>81039000</v>
+        <v>90215000</v>
       </c>
       <c r="AG3" t="n">
-        <v>107530000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>10700000</v>
-      </c>
+        <v>133352000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>278026000</v>
+        <v>172800000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>217369000</v>
+        <v>89155000</v>
       </c>
       <c r="AK3" t="n">
-        <v>17070000</v>
+        <v>19499000</v>
       </c>
       <c r="AL3" t="n">
-        <v>43587000</v>
+        <v>64146000</v>
       </c>
       <c r="AM3" t="n">
-        <v>922564000</v>
+        <v>1264286000</v>
       </c>
       <c r="AN3" t="n">
-        <v>377040000</v>
+        <v>601507000</v>
       </c>
       <c r="AO3" t="n">
-        <v>17450000</v>
+        <v>16274000</v>
       </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="AT3" t="n">
-        <v>294565000</v>
+        <v>465405000</v>
       </c>
       <c r="AU3" t="n">
-        <v>48840000</v>
+        <v>71584000</v>
       </c>
       <c r="AV3" t="n">
-        <v>245725000</v>
+        <v>393821000</v>
       </c>
       <c r="AW3" t="n">
-        <v>65025000</v>
+        <v>119673000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-225655000</v>
+        <v>-171098000</v>
       </c>
       <c r="AY3" t="n">
-        <v>290680000</v>
+        <v>290771000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>281547000</v>
+        <v>282688000</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>9133000</v>
+        <v>8083000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>545524000</v>
+        <v>662779000</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>3576000</v>
       </c>
       <c r="BF3" t="n">
-        <v>42791000</v>
+        <v>70922000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1368000</v>
+        <v>16777000</v>
       </c>
       <c r="BH3" t="n">
-        <v>322060000</v>
+        <v>327422000</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>322060000</v>
+        <v>327422000</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
-        <v>36283000</v>
+        <v>32672000</v>
       </c>
       <c r="BN3" t="n">
-        <v>5838000</v>
+        <v>5664000</v>
       </c>
       <c r="BO3" t="n">
-        <v>30613000</v>
+        <v>87965000</v>
       </c>
       <c r="BP3" t="n">
-        <v>-1109000</v>
+        <v>-3304000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>31722000</v>
+        <v>91269000</v>
       </c>
       <c r="BR3" t="n">
-        <v>106571000</v>
+        <v>117781000</v>
       </c>
       <c r="BS3" t="n">
-        <v>21463000</v>
+        <v>14319000</v>
       </c>
       <c r="BT3" t="n">
-        <v>85108000</v>
+        <v>103462000</v>
       </c>
       <c r="BU3" t="n">
-        <v>85108000</v>
+        <v>103462000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>2595613733</v>
@@ -2048,46 +2062,50 @@
         <v>2595613733</v>
       </c>
       <c r="D4" t="n">
-        <v>60567000</v>
+        <v>96582000</v>
       </c>
       <c r="E4" t="n">
-        <v>342930000</v>
+        <v>271818000</v>
       </c>
       <c r="F4" t="n">
-        <v>-122478000</v>
+        <v>-180790000</v>
       </c>
       <c r="G4" t="n">
-        <v>506956000</v>
+        <v>295465000</v>
       </c>
       <c r="H4" t="n">
-        <v>62288000</v>
+        <v>-114400000</v>
       </c>
       <c r="I4" t="n">
-        <v>-122478000</v>
+        <v>-180790000</v>
       </c>
       <c r="J4" t="n">
-        <v>178901000</v>
+        <v>90128000</v>
       </c>
       <c r="K4" t="n">
-        <v>342927000</v>
+        <v>113775000</v>
       </c>
       <c r="L4" t="n">
-        <v>373604000</v>
+        <v>187935000</v>
       </c>
       <c r="M4" t="n">
-        <v>399027000</v>
+        <v>167181000</v>
       </c>
       <c r="N4" t="n">
-        <v>56100000</v>
+        <v>53406000</v>
       </c>
       <c r="O4" t="n">
-        <v>342927000</v>
+        <v>113775000</v>
       </c>
       <c r="P4" t="n">
-        <v>464612000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+        <v>448062000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-852679000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>521046000</v>
+      </c>
       <c r="S4" t="n">
         <v>6489000</v>
       </c>
@@ -2095,154 +2113,152 @@
         <v>6489000</v>
       </c>
       <c r="U4" t="n">
-        <v>865259000</v>
+        <v>755383000</v>
       </c>
       <c r="V4" t="n">
-        <v>264768000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>127509000</v>
-      </c>
+        <v>95459000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>17896000</v>
+        <v>12210000</v>
       </c>
       <c r="Z4" t="n">
-        <v>119363000</v>
+        <v>83249000</v>
       </c>
       <c r="AA4" t="n">
-        <v>88686000</v>
+        <v>9089000</v>
       </c>
       <c r="AB4" t="n">
-        <v>30677000</v>
+        <v>74160000</v>
       </c>
       <c r="AC4" t="n">
-        <v>600491000</v>
+        <v>659924000</v>
       </c>
       <c r="AD4" t="n">
-        <v>37300000</v>
+        <v>34430000</v>
       </c>
       <c r="AE4" t="n">
-        <v>223567000</v>
+        <v>188569000</v>
       </c>
       <c r="AF4" t="n">
-        <v>90215000</v>
+        <v>81039000</v>
       </c>
       <c r="AG4" t="n">
-        <v>133352000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>107530000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>10700000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>172800000</v>
+        <v>278026000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>89155000</v>
+        <v>217369000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19499000</v>
+        <v>17070000</v>
       </c>
       <c r="AL4" t="n">
-        <v>64146000</v>
+        <v>43587000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1264286000</v>
+        <v>922564000</v>
       </c>
       <c r="AN4" t="n">
-        <v>601507000</v>
+        <v>377040000</v>
       </c>
       <c r="AO4" t="n">
-        <v>16274000</v>
+        <v>17450000</v>
       </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>155000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>155000</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>465405000</v>
+        <v>294565000</v>
       </c>
       <c r="AU4" t="n">
-        <v>71584000</v>
+        <v>48840000</v>
       </c>
       <c r="AV4" t="n">
-        <v>393821000</v>
+        <v>245725000</v>
       </c>
       <c r="AW4" t="n">
-        <v>119673000</v>
+        <v>65025000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-171098000</v>
+        <v>-225655000</v>
       </c>
       <c r="AY4" t="n">
-        <v>290771000</v>
+        <v>290680000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>282688000</v>
+        <v>281547000</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>8083000</v>
+        <v>9133000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>662779000</v>
+        <v>545524000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3576000</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>70922000</v>
+        <v>42791000</v>
       </c>
       <c r="BG4" t="n">
-        <v>16777000</v>
+        <v>1368000</v>
       </c>
       <c r="BH4" t="n">
-        <v>327422000</v>
+        <v>322060000</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>327422000</v>
+        <v>322060000</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>32672000</v>
+        <v>36283000</v>
       </c>
       <c r="BN4" t="n">
-        <v>5664000</v>
+        <v>5838000</v>
       </c>
       <c r="BO4" t="n">
-        <v>87965000</v>
+        <v>30613000</v>
       </c>
       <c r="BP4" t="n">
-        <v>-3304000</v>
+        <v>-1109000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>91269000</v>
+        <v>31722000</v>
       </c>
       <c r="BR4" t="n">
-        <v>117781000</v>
+        <v>106571000</v>
       </c>
       <c r="BS4" t="n">
-        <v>14319000</v>
+        <v>21463000</v>
       </c>
       <c r="BT4" t="n">
-        <v>103462000</v>
+        <v>85108000</v>
       </c>
       <c r="BU4" t="n">
-        <v>103462000</v>
+        <v>85108000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
         <v>2595613733</v>
@@ -2251,46 +2267,50 @@
         <v>2595613733</v>
       </c>
       <c r="D5" t="n">
-        <v>247874000</v>
+        <v>106823000</v>
       </c>
       <c r="E5" t="n">
-        <v>576365000</v>
+        <v>175102000</v>
       </c>
       <c r="F5" t="n">
-        <v>-369623000</v>
+        <v>-247735000</v>
       </c>
       <c r="G5" t="n">
-        <v>546762000</v>
+        <v>-60973000</v>
       </c>
       <c r="H5" t="n">
-        <v>-31314000</v>
+        <v>-140876000</v>
       </c>
       <c r="I5" t="n">
-        <v>-369623000</v>
+        <v>-247735000</v>
       </c>
       <c r="J5" t="n">
-        <v>224668000</v>
+        <v>9291000</v>
       </c>
       <c r="K5" t="n">
-        <v>195065000</v>
+        <v>-226784000</v>
       </c>
       <c r="L5" t="n">
-        <v>453898000</v>
+        <v>-154914000</v>
       </c>
       <c r="M5" t="n">
-        <v>249808000</v>
+        <v>-185098000</v>
       </c>
       <c r="N5" t="n">
-        <v>54743000</v>
+        <v>41686000</v>
       </c>
       <c r="O5" t="n">
-        <v>195065000</v>
+        <v>-226784000</v>
       </c>
       <c r="P5" t="n">
-        <v>204600000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>457862000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1203189000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>521046000</v>
+      </c>
       <c r="S5" t="n">
         <v>6489000</v>
       </c>
@@ -2298,161 +2318,141 @@
         <v>6489000</v>
       </c>
       <c r="U5" t="n">
-        <v>1381072000</v>
+        <v>580486000</v>
       </c>
       <c r="V5" t="n">
-        <v>512074000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>71248000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>383000</v>
-      </c>
+        <v>74778000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>21215000</v>
+        <v>323000</v>
       </c>
       <c r="Z5" t="n">
-        <v>419611000</v>
+        <v>74455000</v>
       </c>
       <c r="AA5" t="n">
-        <v>160778000</v>
+        <v>2585000</v>
       </c>
       <c r="AB5" t="n">
-        <v>258833000</v>
+        <v>71870000</v>
       </c>
       <c r="AC5" t="n">
-        <v>868998000</v>
+        <v>505708000</v>
       </c>
       <c r="AD5" t="n">
-        <v>38256000</v>
+        <v>34112000</v>
       </c>
       <c r="AE5" t="n">
-        <v>156754000</v>
+        <v>100647000</v>
       </c>
       <c r="AF5" t="n">
-        <v>63890000</v>
+        <v>6706000</v>
       </c>
       <c r="AG5" t="n">
-        <v>92864000</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>93941000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16791000</v>
+      </c>
       <c r="AI5" t="n">
-        <v>286995000</v>
+        <v>250855000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>188965000</v>
+        <v>186312000</v>
       </c>
       <c r="AK5" t="n">
-        <v>9797000</v>
+        <v>12361000</v>
       </c>
       <c r="AL5" t="n">
-        <v>88233000</v>
+        <v>52182000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1630880000</v>
+        <v>395388000</v>
       </c>
       <c r="AN5" t="n">
-        <v>793196000</v>
+        <v>30556000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15089000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>20332000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>155000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>155000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>564688000</v>
+        <v>20951000</v>
       </c>
       <c r="AU5" t="n">
-        <v>91325000</v>
+        <v>1293000</v>
       </c>
       <c r="AV5" t="n">
-        <v>473363000</v>
+        <v>19658000</v>
       </c>
       <c r="AW5" t="n">
-        <v>171932000</v>
+        <v>9605000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-126753000</v>
+        <v>-280005000</v>
       </c>
       <c r="AY5" t="n">
-        <v>298685000</v>
+        <v>289610000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>281019000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14120000</v>
-      </c>
+        <v>281032000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>17666000</v>
+        <v>8578000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>837684000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
+        <v>364832000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>3566000</v>
+        <v>21212000</v>
       </c>
       <c r="BG5" t="n">
-        <v>21809000</v>
+        <v>11166000</v>
       </c>
       <c r="BH5" t="n">
-        <v>522643000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3863000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
+        <v>143708000</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="n">
-        <v>518780000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>3863000</v>
-      </c>
+        <v>143708000</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>70897000</v>
+        <v>60773000</v>
       </c>
       <c r="BN5" t="n">
-        <v>26343000</v>
+        <v>5447000</v>
       </c>
       <c r="BO5" t="n">
-        <v>76329000</v>
+        <v>53382000</v>
       </c>
       <c r="BP5" t="n">
-        <v>-1982000</v>
+        <v>-1011000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>78311000</v>
+        <v>54393000</v>
       </c>
       <c r="BR5" t="n">
-        <v>116097000</v>
+        <v>69144000</v>
       </c>
       <c r="BS5" t="n">
-        <v>12274000</v>
+        <v>10156000</v>
       </c>
       <c r="BT5" t="n">
-        <v>103823000</v>
+        <v>58988000</v>
       </c>
       <c r="BU5" t="n">
-        <v>103823000</v>
+        <v>58988000</v>
       </c>
     </row>
   </sheetData>
@@ -2713,566 +2713,566 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>32944000</v>
+        <v>121084000</v>
       </c>
       <c r="C2" t="n">
-        <v>-76092000</v>
+        <v>-100116000</v>
       </c>
       <c r="D2" t="n">
-        <v>52622000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>162402000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-107000</v>
+      </c>
       <c r="F2" t="n">
-        <v>58988000</v>
+        <v>103823000</v>
       </c>
       <c r="G2" t="n">
-        <v>85108000</v>
+        <v>112263000</v>
       </c>
       <c r="H2" t="n">
-        <v>-858000</v>
+        <v>9316000</v>
       </c>
       <c r="I2" t="n">
-        <v>-25262000</v>
+        <v>-17756000</v>
       </c>
       <c r="J2" t="n">
-        <v>-92743000</v>
+        <v>-44993000</v>
       </c>
       <c r="K2" t="n">
-        <v>9800000</v>
+        <v>8417000</v>
       </c>
       <c r="L2" t="n">
-        <v>-4515000</v>
+        <v>-56427000</v>
       </c>
       <c r="M2" t="n">
-        <v>-23470000</v>
+        <v>62286000</v>
       </c>
       <c r="N2" t="n">
-        <v>-45055000</v>
+        <v>27097000</v>
       </c>
       <c r="O2" t="n">
-        <v>-74911000</v>
+        <v>-72023000</v>
       </c>
       <c r="P2" t="n">
-        <v>29856000</v>
+        <v>99120000</v>
       </c>
       <c r="Q2" t="n">
-        <v>21585000</v>
+        <v>62286000</v>
       </c>
       <c r="R2" t="n">
-        <v>-1181000</v>
+        <v>-100116000</v>
       </c>
       <c r="S2" t="n">
-        <v>22766000</v>
+        <v>162402000</v>
       </c>
       <c r="T2" t="n">
-        <v>34537000</v>
+        <v>-93954000</v>
       </c>
       <c r="U2" t="n">
-        <v>21574000</v>
+        <v>-115795000</v>
       </c>
       <c r="V2" t="n">
-        <v>259000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>1038000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>12704000</v>
+        <v>-4517000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12704000</v>
+        <v>7552000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-12069000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>28188000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>84828000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-56640000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-107000</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-107000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>32944000</v>
+        <v>121191000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-120000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-3125000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-724000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>37453000</v>
+        <v>32845000</v>
       </c>
       <c r="AK2" t="n">
-        <v>87677000</v>
+        <v>-44899000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4202000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+        <v>124142000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-724000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-2984000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>-46022000</v>
+        <v>-43414000</v>
       </c>
       <c r="AP2" t="n">
-        <v>18095000</v>
+        <v>65076000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>70530000</v>
+        <v>132831000</v>
       </c>
       <c r="AR2" t="n">
-        <v>14695000</v>
+        <v>17557000</v>
       </c>
       <c r="AS2" t="n">
-        <v>55835000</v>
+        <v>115274000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1493000</v>
+        <v>-4781000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-667000</v>
+        <v>-114566000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-372985000</v>
+        <v>13671000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>59363000</v>
+        <v>54574000</v>
       </c>
       <c r="C3" t="n">
-        <v>-113985000</v>
+        <v>-74064000</v>
       </c>
       <c r="D3" t="n">
-        <v>122447000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>77820000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1990000</v>
+      </c>
       <c r="F3" t="n">
-        <v>85108000</v>
+        <v>103462000</v>
       </c>
       <c r="G3" t="n">
-        <v>103462000</v>
+        <v>103823000</v>
       </c>
       <c r="H3" t="n">
-        <v>-5941000</v>
+        <v>-5373000</v>
       </c>
       <c r="I3" t="n">
-        <v>-12413000</v>
+        <v>5012000</v>
       </c>
       <c r="J3" t="n">
-        <v>-92731000</v>
+        <v>-7796000</v>
       </c>
       <c r="K3" t="n">
-        <v>950000</v>
+        <v>53000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-12165000</v>
+        <v>-15241000</v>
       </c>
       <c r="M3" t="n">
-        <v>8462000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-4838000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-78289000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>73451000</v>
-      </c>
+        <v>3756000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>13300000</v>
+        <v>3756000</v>
       </c>
       <c r="R3" t="n">
-        <v>-35696000</v>
+        <v>-74064000</v>
       </c>
       <c r="S3" t="n">
-        <v>48996000</v>
+        <v>77820000</v>
       </c>
       <c r="T3" t="n">
-        <v>20955000</v>
+        <v>-43756000</v>
       </c>
       <c r="U3" t="n">
-        <v>26916000</v>
+        <v>-53988000</v>
       </c>
       <c r="V3" t="n">
-        <v>997000</v>
+        <v>636000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-8007000</v>
+        <v>10941000</v>
       </c>
       <c r="Y3" t="n">
-        <v>843000</v>
+        <v>10941000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-8850000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1925000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>-1925000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>274000</v>
+        <v>-1345000</v>
       </c>
       <c r="AE3" t="n">
-        <v>274000</v>
+        <v>645000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-1990000</v>
       </c>
       <c r="AG3" t="n">
-        <v>59363000</v>
+        <v>56564000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2862000</v>
+        <v>-2100000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1176000</v>
+        <v>-1185000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>35657000</v>
+        <v>-39966000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-38262000</v>
+        <v>-10525000</v>
       </c>
       <c r="AL3" t="n">
-        <v>15288000</v>
+        <v>-74440000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>3863000</v>
       </c>
       <c r="AO3" t="n">
-        <v>58631000</v>
+        <v>41136000</v>
       </c>
       <c r="AP3" t="n">
-        <v>25090000</v>
+        <v>21126000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>73914000</v>
+        <v>76558000</v>
       </c>
       <c r="AR3" t="n">
-        <v>17876000</v>
+        <v>19313000</v>
       </c>
       <c r="AS3" t="n">
-        <v>56038000</v>
+        <v>57245000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1266000</v>
+        <v>15726000</v>
       </c>
       <c r="AU3" t="n">
-        <v>95000</v>
+        <v>-79000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-14180000</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-187780000</v>
+        <v>-82166000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>54574000</v>
+        <v>59363000</v>
       </c>
       <c r="C4" t="n">
-        <v>-74064000</v>
+        <v>-113985000</v>
       </c>
       <c r="D4" t="n">
-        <v>77820000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1990000</v>
-      </c>
+        <v>122447000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>85108000</v>
+      </c>
+      <c r="G4" t="n">
         <v>103462000</v>
       </c>
-      <c r="G4" t="n">
-        <v>103823000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-5373000</v>
+        <v>-5941000</v>
       </c>
       <c r="I4" t="n">
-        <v>5012000</v>
+        <v>-12413000</v>
       </c>
       <c r="J4" t="n">
-        <v>-7796000</v>
+        <v>-92731000</v>
       </c>
       <c r="K4" t="n">
-        <v>53000000</v>
+        <v>950000</v>
       </c>
       <c r="L4" t="n">
-        <v>-15241000</v>
+        <v>-12165000</v>
       </c>
       <c r="M4" t="n">
-        <v>3756000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>8462000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-4838000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-78289000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>73451000</v>
+      </c>
       <c r="Q4" t="n">
-        <v>3756000</v>
+        <v>13300000</v>
       </c>
       <c r="R4" t="n">
-        <v>-74064000</v>
+        <v>-35696000</v>
       </c>
       <c r="S4" t="n">
-        <v>77820000</v>
+        <v>48996000</v>
       </c>
       <c r="T4" t="n">
-        <v>-43756000</v>
+        <v>20955000</v>
       </c>
       <c r="U4" t="n">
-        <v>-53988000</v>
+        <v>26916000</v>
       </c>
       <c r="V4" t="n">
-        <v>636000</v>
+        <v>997000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>10941000</v>
+        <v>-8007000</v>
       </c>
       <c r="Y4" t="n">
-        <v>10941000</v>
+        <v>843000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-8850000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>-1925000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-1925000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1345000</v>
+        <v>274000</v>
       </c>
       <c r="AE4" t="n">
-        <v>645000</v>
+        <v>274000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1990000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>56564000</v>
+        <v>59363000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2100000</v>
+        <v>-2862000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1185000</v>
+        <v>-1176000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-39966000</v>
+        <v>35657000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-10525000</v>
+        <v>-38262000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-74440000</v>
+        <v>15288000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>3863000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>41136000</v>
+        <v>58631000</v>
       </c>
       <c r="AP4" t="n">
-        <v>21126000</v>
+        <v>25090000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>76558000</v>
+        <v>73914000</v>
       </c>
       <c r="AR4" t="n">
-        <v>19313000</v>
+        <v>17876000</v>
       </c>
       <c r="AS4" t="n">
-        <v>57245000</v>
+        <v>56038000</v>
       </c>
       <c r="AT4" t="n">
-        <v>15726000</v>
+        <v>1266000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-79000</v>
+        <v>95000</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-14180000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-82166000</v>
+        <v>-187780000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>121084000</v>
+        <v>32944000</v>
       </c>
       <c r="C5" t="n">
-        <v>-100116000</v>
+        <v>-76092000</v>
       </c>
       <c r="D5" t="n">
-        <v>162402000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-107000</v>
-      </c>
+        <v>52622000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>103823000</v>
+        <v>58988000</v>
       </c>
       <c r="G5" t="n">
-        <v>112263000</v>
+        <v>85108000</v>
       </c>
       <c r="H5" t="n">
-        <v>9316000</v>
+        <v>-858000</v>
       </c>
       <c r="I5" t="n">
-        <v>-17756000</v>
+        <v>-25262000</v>
       </c>
       <c r="J5" t="n">
-        <v>-44993000</v>
+        <v>-92743000</v>
       </c>
       <c r="K5" t="n">
-        <v>8417000</v>
+        <v>9800000</v>
       </c>
       <c r="L5" t="n">
-        <v>-56427000</v>
+        <v>-4515000</v>
       </c>
       <c r="M5" t="n">
-        <v>62286000</v>
+        <v>-23470000</v>
       </c>
       <c r="N5" t="n">
-        <v>27097000</v>
+        <v>-45055000</v>
       </c>
       <c r="O5" t="n">
-        <v>-72023000</v>
+        <v>-74911000</v>
       </c>
       <c r="P5" t="n">
-        <v>99120000</v>
+        <v>29856000</v>
       </c>
       <c r="Q5" t="n">
-        <v>62286000</v>
+        <v>21585000</v>
       </c>
       <c r="R5" t="n">
-        <v>-100116000</v>
+        <v>-1181000</v>
       </c>
       <c r="S5" t="n">
-        <v>162402000</v>
+        <v>22766000</v>
       </c>
       <c r="T5" t="n">
-        <v>-93954000</v>
+        <v>34537000</v>
       </c>
       <c r="U5" t="n">
-        <v>-115795000</v>
+        <v>21574000</v>
       </c>
       <c r="V5" t="n">
-        <v>1038000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>259000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-4517000</v>
+        <v>12704000</v>
       </c>
       <c r="Y5" t="n">
-        <v>7552000</v>
+        <v>12704000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-12069000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>28188000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>84828000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-56640000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-107000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" t="n">
-        <v>-107000</v>
-      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>121191000</v>
+        <v>32944000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3125000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-724000</v>
-      </c>
+        <v>-120000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>32845000</v>
+        <v>37453000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-44899000</v>
+        <v>87677000</v>
       </c>
       <c r="AL5" t="n">
-        <v>124142000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-724000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-2984000</v>
-      </c>
+        <v>-4202000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>-43414000</v>
+        <v>-46022000</v>
       </c>
       <c r="AP5" t="n">
-        <v>65076000</v>
+        <v>18095000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>132831000</v>
+        <v>70530000</v>
       </c>
       <c r="AR5" t="n">
-        <v>17557000</v>
+        <v>14695000</v>
       </c>
       <c r="AS5" t="n">
-        <v>115274000</v>
+        <v>55835000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-4781000</v>
+        <v>-1493000</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-114566000</v>
+        <v>-667000</v>
       </c>
       <c r="AW5" t="n">
-        <v>13671000</v>
+        <v>-372985000</v>
       </c>
     </row>
   </sheetData>
@@ -3777,192 +3777,192 @@
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.389</v>
+        <v>0.372</v>
       </c>
       <c r="AD2" t="n">
         <v>1672000</v>
@@ -4141,7 +4141,7 @@
         <v>0.027</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.028885</v>
+        <v>0.02788</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4211,10 +4211,10 @@
         <v>-1.319</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.3076923</v>
+        <v>-0.35714287</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -4315,143 +4315,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CT2" t="n">
+        <v>0.0020000003</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.025 - 0.028</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>TRANSMIT ENT</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Transmit Entertainment Limited</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.0030000005</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.12500001</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>0.024 - 0.055</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.027999999</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.5090909</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-35.714287</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1740472206</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1740472206</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.00087999925</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.03156382</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.1011236</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>1759219139</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>8.000000999999999</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>finmb_222706829</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="CX2" t="n">
+      <c r="EA2" t="n">
         <v>28800000</v>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>8.000000999999999</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.12500001</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>0.024 - 0.055</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.027999999</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.5090909</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-30.76923</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1740472206</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1740472206</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.0018849988</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.06525874</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.1011236</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
         <v>1351647000000</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.0020000003</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>0.025 - 0.028</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.0030000005</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>1759219139</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>TRANSMIT ENT</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Transmit Entertainment Limited</t>
-        </is>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
